--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,6 +648,96 @@
         </is>
       </c>
       <c r="AB2" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>16:29:00</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7961</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9393</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.352</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2628</v>
+      </c>
+      <c r="J3" t="n">
+        <v>123</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>3141</v>
+      </c>
+      <c r="M3" t="n">
+        <v>71</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>79044</v>
+      </c>
+      <c r="P3" t="n">
+        <v>58450</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R3" t="n">
+        <v>15524</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>14544</v>
+      </c>
+      <c r="U3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,6 +738,96 @@
         </is>
       </c>
       <c r="AB3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>16:30:01</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7955</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9384</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2680</v>
+      </c>
+      <c r="J4" t="n">
+        <v>52</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>3218</v>
+      </c>
+      <c r="M4" t="n">
+        <v>77</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>78566</v>
+      </c>
+      <c r="P4" t="n">
+        <v>59169</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R4" t="n">
+        <v>15514</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>15007</v>
+      </c>
+      <c r="U4" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,6 +828,96 @@
         </is>
       </c>
       <c r="AB4" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>16:31:02</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7957</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9402</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2719</v>
+      </c>
+      <c r="J5" t="n">
+        <v>39</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>3231</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>78527</v>
+      </c>
+      <c r="P5" t="n">
+        <v>59833</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>15604</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>15380</v>
+      </c>
+      <c r="U5" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +918,96 @@
         </is>
       </c>
       <c r="AB5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>16:32:03</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7966</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9365</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2776</v>
+      </c>
+      <c r="J6" t="n">
+        <v>57</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>3262</v>
+      </c>
+      <c r="M6" t="n">
+        <v>31</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>78772</v>
+      </c>
+      <c r="P6" t="n">
+        <v>60007</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>15670</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>15502</v>
+      </c>
+      <c r="U6" t="n">
+        <v>62</v>
+      </c>
+      <c r="W6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,6 +1008,96 @@
         </is>
       </c>
       <c r="AB6" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>16:33:04</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7948</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9390</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2762</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>3312</v>
+      </c>
+      <c r="M7" t="n">
+        <v>50</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>78814</v>
+      </c>
+      <c r="P7" t="n">
+        <v>59921</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R7" t="n">
+        <v>15626</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>15432</v>
+      </c>
+      <c r="U7" t="n">
+        <v>62</v>
+      </c>
+      <c r="W7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB7"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1098,96 @@
         </is>
       </c>
       <c r="AB7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>16:34:05</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7948</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9382</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.311</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2781</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>3402</v>
+      </c>
+      <c r="M8" t="n">
+        <v>90</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>78912</v>
+      </c>
+      <c r="P8" t="n">
+        <v>60191</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R8" t="n">
+        <v>15726</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>15511</v>
+      </c>
+      <c r="U8" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB8"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,6 +1188,96 @@
         </is>
       </c>
       <c r="AB8" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>16:35:06</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7953</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9375</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2857</v>
+      </c>
+      <c r="J9" t="n">
+        <v>76</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>3388</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-14</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>79155</v>
+      </c>
+      <c r="P9" t="n">
+        <v>60307</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R9" t="n">
+        <v>15750</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>15576</v>
+      </c>
+      <c r="U9" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,6 +1278,96 @@
         </is>
       </c>
       <c r="AB9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>16:36:07</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7960</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9351</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2904</v>
+      </c>
+      <c r="J10" t="n">
+        <v>47</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>3436</v>
+      </c>
+      <c r="M10" t="n">
+        <v>48</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>79398</v>
+      </c>
+      <c r="P10" t="n">
+        <v>60401</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R10" t="n">
+        <v>15763</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>15679</v>
+      </c>
+      <c r="U10" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="W10" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1368,6 +1368,96 @@
         </is>
       </c>
       <c r="AB10" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>16:37:08</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7958</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9354</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2975</v>
+      </c>
+      <c r="J11" t="n">
+        <v>71</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>3452</v>
+      </c>
+      <c r="M11" t="n">
+        <v>16</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>79625</v>
+      </c>
+      <c r="P11" t="n">
+        <v>60571</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R11" t="n">
+        <v>15811</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T11" t="n">
+        <v>15732</v>
+      </c>
+      <c r="U11" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="W11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1458,6 +1458,96 @@
         </is>
       </c>
       <c r="AB11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>16:38:09</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7958</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9353</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3011</v>
+      </c>
+      <c r="J12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>3495</v>
+      </c>
+      <c r="M12" t="n">
+        <v>43</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>79785</v>
+      </c>
+      <c r="P12" t="n">
+        <v>60731</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R12" t="n">
+        <v>15818</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T12" t="n">
+        <v>15735</v>
+      </c>
+      <c r="U12" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1548,6 +1548,96 @@
         </is>
       </c>
       <c r="AB12" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>16:39:11</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7965</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9368</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3008</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>3440</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-55</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>80106</v>
+      </c>
+      <c r="P13" t="n">
+        <v>60362</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R13" t="n">
+        <v>15825</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T13" t="n">
+        <v>15674</v>
+      </c>
+      <c r="U13" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1638,6 +1638,96 @@
         </is>
       </c>
       <c r="AB13" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>16:40:12</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7966</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9371</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3049</v>
+      </c>
+      <c r="J14" t="n">
+        <v>41</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>3459</v>
+      </c>
+      <c r="M14" t="n">
+        <v>19</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>80118</v>
+      </c>
+      <c r="P14" t="n">
+        <v>60638</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R14" t="n">
+        <v>15758</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T14" t="n">
+        <v>15788</v>
+      </c>
+      <c r="U14" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB14"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,6 +1728,96 @@
         </is>
       </c>
       <c r="AB14" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>16:41:13</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7968</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9359</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3081</v>
+      </c>
+      <c r="J15" t="n">
+        <v>32</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>3444</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-15</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>80499</v>
+      </c>
+      <c r="P15" t="n">
+        <v>60614</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R15" t="n">
+        <v>15771</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T15" t="n">
+        <v>15713</v>
+      </c>
+      <c r="U15" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1818,6 +1818,96 @@
         </is>
       </c>
       <c r="AB15" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>16:42:14</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7971</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9347</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3077</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>3432</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-12</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>80355</v>
+      </c>
+      <c r="P16" t="n">
+        <v>60626</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R16" t="n">
+        <v>15814</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T16" t="n">
+        <v>15733</v>
+      </c>
+      <c r="U16" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AB17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1908,6 +1908,96 @@
         </is>
       </c>
       <c r="AB16" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16:43:15</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7970</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9354</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3175</v>
+      </c>
+      <c r="J17" t="n">
+        <v>98</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>3487</v>
+      </c>
+      <c r="M17" t="n">
+        <v>55</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>80640</v>
+      </c>
+      <c r="P17" t="n">
+        <v>60951</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R17" t="n">
+        <v>15834</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T17" t="n">
+        <v>15898</v>
+      </c>
+      <c r="U17" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB17"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1998,6 +1998,96 @@
         </is>
       </c>
       <c r="AB17" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>16:44:16</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7957</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9363</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3163</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>3554</v>
+      </c>
+      <c r="M18" t="n">
+        <v>67</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>80448</v>
+      </c>
+      <c r="P18" t="n">
+        <v>61481</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R18" t="n">
+        <v>15877</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T18" t="n">
+        <v>16106</v>
+      </c>
+      <c r="U18" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB18"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2088,6 +2088,96 @@
         </is>
       </c>
       <c r="AB18" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>16:45:17</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7954</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9366</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3051</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-112</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>3599</v>
+      </c>
+      <c r="M19" t="n">
+        <v>45</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>80423</v>
+      </c>
+      <c r="P19" t="n">
+        <v>61671</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R19" t="n">
+        <v>15915</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T19" t="n">
+        <v>16115</v>
+      </c>
+      <c r="U19" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2178,6 +2178,90 @@
         </is>
       </c>
       <c r="AB19" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>16:46:06</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7962</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9363</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="H20" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3068</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>3602</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>80618</v>
+      </c>
+      <c r="P20" t="n">
+        <v>61656</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R20" t="n">
+        <v>15955</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T20" t="n">
+        <v>16114</v>
+      </c>
+      <c r="U20" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2262,6 +2262,96 @@
         </is>
       </c>
       <c r="AB20" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>16:47:08</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7967</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9365</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3102</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>3557</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-45</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>80768</v>
+      </c>
+      <c r="P21" t="n">
+        <v>61653</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R21" t="n">
+        <v>15961</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T21" t="n">
+        <v>16190</v>
+      </c>
+      <c r="U21" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2352,6 +2352,96 @@
         </is>
       </c>
       <c r="AB21" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>16:48:09</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7961</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9366</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3121</v>
+      </c>
+      <c r="J22" t="n">
+        <v>19</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>3581</v>
+      </c>
+      <c r="M22" t="n">
+        <v>24</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>80805</v>
+      </c>
+      <c r="P22" t="n">
+        <v>61822</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R22" t="n">
+        <v>15968</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T22" t="n">
+        <v>16230</v>
+      </c>
+      <c r="U22" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB22"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2442,6 +2442,96 @@
         </is>
       </c>
       <c r="AB22" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16:49:10</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7959</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9365</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3144</v>
+      </c>
+      <c r="J23" t="n">
+        <v>23</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>3607</v>
+      </c>
+      <c r="M23" t="n">
+        <v>26</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>80965</v>
+      </c>
+      <c r="P23" t="n">
+        <v>61982</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R23" t="n">
+        <v>15965</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T23" t="n">
+        <v>16316</v>
+      </c>
+      <c r="U23" t="n">
+        <v>61</v>
+      </c>
+      <c r="W23" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2532,6 +2532,96 @@
         </is>
       </c>
       <c r="AB23" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16:50:11</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7955</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9354</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3134</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>3680</v>
+      </c>
+      <c r="M24" t="n">
+        <v>73</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>80939</v>
+      </c>
+      <c r="P24" t="n">
+        <v>62326</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R24" t="n">
+        <v>15952</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T24" t="n">
+        <v>16469</v>
+      </c>
+      <c r="U24" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2622,6 +2622,96 @@
         </is>
       </c>
       <c r="AB24" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16:51:13</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7952</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9358</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="H25" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3129</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>3698</v>
+      </c>
+      <c r="M25" t="n">
+        <v>18</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>80935</v>
+      </c>
+      <c r="P25" t="n">
+        <v>62371</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R25" t="n">
+        <v>15990</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T25" t="n">
+        <v>16418</v>
+      </c>
+      <c r="U25" t="n">
+        <v>61</v>
+      </c>
+      <c r="W25" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB25"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,6 +2712,96 @@
         </is>
       </c>
       <c r="AB25" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16:52:14</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7957</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9339</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3128</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>3714</v>
+      </c>
+      <c r="M26" t="n">
+        <v>16</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>81140</v>
+      </c>
+      <c r="P26" t="n">
+        <v>62257</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R26" t="n">
+        <v>16051</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T26" t="n">
+        <v>16415</v>
+      </c>
+      <c r="U26" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2802,6 +2802,96 @@
         </is>
       </c>
       <c r="AB26" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>16:53:15</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7957</v>
+      </c>
+      <c r="E27" t="n">
+        <v>9342</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="H27" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3125</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>3740</v>
+      </c>
+      <c r="M27" t="n">
+        <v>26</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>81184</v>
+      </c>
+      <c r="P27" t="n">
+        <v>62388</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R27" t="n">
+        <v>16048</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T27" t="n">
+        <v>16475</v>
+      </c>
+      <c r="U27" t="n">
+        <v>61</v>
+      </c>
+      <c r="W27" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB27"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2892,6 +2892,90 @@
         </is>
       </c>
       <c r="AB27" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16:54:13</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7954</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9343</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3129</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>3750</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>81157</v>
+      </c>
+      <c r="P28" t="n">
+        <v>62410</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R28" t="n">
+        <v>16072</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T28" t="n">
+        <v>16518</v>
+      </c>
+      <c r="U28" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="W28" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X28" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2976,6 +2976,96 @@
         </is>
       </c>
       <c r="AB28" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16:55:14</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7956</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9343</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3153</v>
+      </c>
+      <c r="J29" t="n">
+        <v>24</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>3743</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>81263</v>
+      </c>
+      <c r="P29" t="n">
+        <v>62413</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R29" t="n">
+        <v>16087</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T29" t="n">
+        <v>16543</v>
+      </c>
+      <c r="U29" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="W29" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB29"/>
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3066,6 +3066,96 @@
         </is>
       </c>
       <c r="AB29" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16:56:16</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7951</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9344</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3151</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>3808</v>
+      </c>
+      <c r="M30" t="n">
+        <v>65</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>81127</v>
+      </c>
+      <c r="P30" t="n">
+        <v>62615</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R30" t="n">
+        <v>16095</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T30" t="n">
+        <v>16571</v>
+      </c>
+      <c r="U30" t="n">
+        <v>61</v>
+      </c>
+      <c r="W30" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3158,6 +3158,96 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>16:57:17</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D31" t="n">
+        <v>7944</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9313</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3162</v>
+      </c>
+      <c r="J31" t="n">
+        <v>11</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>3651</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-157</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>80944</v>
+      </c>
+      <c r="P31" t="n">
+        <v>61895</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R31" t="n">
+        <v>16063</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T31" t="n">
+        <v>16075</v>
+      </c>
+      <c r="U31" t="n">
+        <v>61</v>
+      </c>
+      <c r="W31" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AB32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3248,6 +3248,96 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>16:58:18</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7945</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9312</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.311</v>
+      </c>
+      <c r="H32" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3187</v>
+      </c>
+      <c r="J32" t="n">
+        <v>25</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>3640</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-11</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>81235</v>
+      </c>
+      <c r="P32" t="n">
+        <v>61952</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R32" t="n">
+        <v>16081</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T32" t="n">
+        <v>16118</v>
+      </c>
+      <c r="U32" t="n">
+        <v>61</v>
+      </c>
+      <c r="W32" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X32" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB32"/>
+  <dimension ref="A1:AB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3336,6 +3336,96 @@
         </is>
       </c>
       <c r="AB32" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>16:59:19</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D33" t="n">
+        <v>7947</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9317</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H33" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3222</v>
+      </c>
+      <c r="J33" t="n">
+        <v>35</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>3640</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>81302</v>
+      </c>
+      <c r="P33" t="n">
+        <v>62050</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R33" t="n">
+        <v>16103</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T33" t="n">
+        <v>16157</v>
+      </c>
+      <c r="U33" t="n">
+        <v>61</v>
+      </c>
+      <c r="W33" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X33" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB33"/>
+  <dimension ref="A1:AB34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3426,6 +3426,96 @@
         </is>
       </c>
       <c r="AB33" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>17:00:20</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7946</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9322</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="H34" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3262</v>
+      </c>
+      <c r="J34" t="n">
+        <v>40</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>3629</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-11</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>81450</v>
+      </c>
+      <c r="P34" t="n">
+        <v>62012</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R34" t="n">
+        <v>16049</v>
+      </c>
+      <c r="S34" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T34" t="n">
+        <v>16094</v>
+      </c>
+      <c r="U34" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="W34" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB34"/>
+  <dimension ref="A1:AB35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3516,6 +3516,96 @@
         </is>
       </c>
       <c r="AB34" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>17:01:21</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7947</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9322</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="H35" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3271</v>
+      </c>
+      <c r="J35" t="n">
+        <v>9</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>3672</v>
+      </c>
+      <c r="M35" t="n">
+        <v>43</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>81629</v>
+      </c>
+      <c r="P35" t="n">
+        <v>62173</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R35" t="n">
+        <v>16093</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T35" t="n">
+        <v>16154</v>
+      </c>
+      <c r="U35" t="n">
+        <v>61</v>
+      </c>
+      <c r="W35" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB35"/>
+  <dimension ref="A1:AB36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3606,6 +3606,96 @@
         </is>
       </c>
       <c r="AB35" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>17:02:22</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7947</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9316</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3288</v>
+      </c>
+      <c r="J36" t="n">
+        <v>17</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>3682</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>81647</v>
+      </c>
+      <c r="P36" t="n">
+        <v>62218</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R36" t="n">
+        <v>16104</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T36" t="n">
+        <v>16197</v>
+      </c>
+      <c r="U36" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="W36" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X36" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:AB37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3698,6 +3698,96 @@
       <c r="AB36" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>17:03:23</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7934</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9316</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3269</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-19</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>3734</v>
+      </c>
+      <c r="M37" t="n">
+        <v>52</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>81507</v>
+      </c>
+      <c r="P37" t="n">
+        <v>62041</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R37" t="n">
+        <v>16118</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T37" t="n">
+        <v>16104</v>
+      </c>
+      <c r="U37" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="W37" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X37" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AB38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +3788,96 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>17:13:51</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7951</v>
+      </c>
+      <c r="E38" t="n">
+        <v>9349</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3236</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-33</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>3806</v>
+      </c>
+      <c r="M38" t="n">
+        <v>72</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>81817</v>
+      </c>
+      <c r="P38" t="n">
+        <v>62262</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R38" t="n">
+        <v>16246</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T38" t="n">
+        <v>16144</v>
+      </c>
+      <c r="U38" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="W38" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X38" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB38"/>
+  <dimension ref="A1:AB39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3876,6 +3876,96 @@
         </is>
       </c>
       <c r="AB38" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>17:17:52</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7967</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9311</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3310</v>
+      </c>
+      <c r="J39" t="n">
+        <v>74</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>3969</v>
+      </c>
+      <c r="M39" t="n">
+        <v>163</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>82152</v>
+      </c>
+      <c r="P39" t="n">
+        <v>62269</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R39" t="n">
+        <v>16394</v>
+      </c>
+      <c r="S39" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T39" t="n">
+        <v>16236</v>
+      </c>
+      <c r="U39" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X39" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB39"/>
+  <dimension ref="A1:AB40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3966,6 +3966,96 @@
         </is>
       </c>
       <c r="AB39" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>17:18:53</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7973</v>
+      </c>
+      <c r="E40" t="n">
+        <v>9302</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="H40" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3352</v>
+      </c>
+      <c r="J40" t="n">
+        <v>42</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>3960</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-9</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>82295</v>
+      </c>
+      <c r="P40" t="n">
+        <v>62274</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R40" t="n">
+        <v>16346</v>
+      </c>
+      <c r="S40" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T40" t="n">
+        <v>16093</v>
+      </c>
+      <c r="U40" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="W40" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X40" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB40"/>
+  <dimension ref="A1:AB41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4056,6 +4056,96 @@
         </is>
       </c>
       <c r="AB40" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>17:19:54</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D41" t="n">
+        <v>7977</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9311</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.146</v>
+      </c>
+      <c r="H41" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10104</v>
+      </c>
+      <c r="J41" t="n">
+        <v>6752</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>16227</v>
+      </c>
+      <c r="M41" t="n">
+        <v>12267</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>80405</v>
+      </c>
+      <c r="P41" t="n">
+        <v>70154</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R41" t="n">
+        <v>16296</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T41" t="n">
+        <v>16227</v>
+      </c>
+      <c r="U41" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="W41" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X41" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB41"/>
+  <dimension ref="A1:AB42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4146,6 +4146,96 @@
         </is>
       </c>
       <c r="AB41" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>17:20:55</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7975</v>
+      </c>
+      <c r="E42" t="n">
+        <v>9304</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.327</v>
+      </c>
+      <c r="H42" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3524</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-6580</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>3900</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-12327</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>82496</v>
+      </c>
+      <c r="P42" t="n">
+        <v>62172</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R42" t="n">
+        <v>16189</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T42" t="n">
+        <v>16209</v>
+      </c>
+      <c r="U42" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="W42" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X42" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB42"/>
+  <dimension ref="A1:AB43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4236,6 +4236,96 @@
         </is>
       </c>
       <c r="AB42" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>17:21:56</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D43" t="n">
+        <v>7979</v>
+      </c>
+      <c r="E43" t="n">
+        <v>9293</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="H43" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I43" t="n">
+        <v>10355</v>
+      </c>
+      <c r="J43" t="n">
+        <v>6831</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>16184</v>
+      </c>
+      <c r="M43" t="n">
+        <v>12284</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>80909</v>
+      </c>
+      <c r="P43" t="n">
+        <v>70010</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R43" t="n">
+        <v>16244</v>
+      </c>
+      <c r="S43" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T43" t="n">
+        <v>16184</v>
+      </c>
+      <c r="U43" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W43" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X43" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB43"/>
+  <dimension ref="A1:AB44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4326,6 +4326,96 @@
         </is>
       </c>
       <c r="AB43" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>17:22:57</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7979</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9314</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H44" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I44" t="n">
+        <v>10362</v>
+      </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>16313</v>
+      </c>
+      <c r="M44" t="n">
+        <v>129</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>80870</v>
+      </c>
+      <c r="P44" t="n">
+        <v>70305</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R44" t="n">
+        <v>16244</v>
+      </c>
+      <c r="S44" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T44" t="n">
+        <v>16313</v>
+      </c>
+      <c r="U44" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W44" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X44" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB44"/>
+  <dimension ref="A1:AB45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4416,6 +4416,90 @@
         </is>
       </c>
       <c r="AB44" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>17:23:52</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D45" t="n">
+        <v>7969</v>
+      </c>
+      <c r="E45" t="n">
+        <v>9321</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H45" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3569</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>3909</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>82626</v>
+      </c>
+      <c r="P45" t="n">
+        <v>62584</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R45" t="n">
+        <v>16193</v>
+      </c>
+      <c r="S45" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T45" t="n">
+        <v>16339</v>
+      </c>
+      <c r="U45" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="W45" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X45" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB45"/>
+  <dimension ref="A1:AB46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4500,6 +4500,96 @@
         </is>
       </c>
       <c r="AB45" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>17:24:53</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7975</v>
+      </c>
+      <c r="E46" t="n">
+        <v>9326</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="H46" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I46" t="n">
+        <v>3599</v>
+      </c>
+      <c r="J46" t="n">
+        <v>30</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>3966</v>
+      </c>
+      <c r="M46" t="n">
+        <v>57</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>83007</v>
+      </c>
+      <c r="P46" t="n">
+        <v>62689</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R46" t="n">
+        <v>16218</v>
+      </c>
+      <c r="S46" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T46" t="n">
+        <v>16339</v>
+      </c>
+      <c r="U46" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="W46" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X46" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB46"/>
+  <dimension ref="A1:AB47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4590,6 +4590,96 @@
         </is>
       </c>
       <c r="AB46" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>17:25:54</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D47" t="n">
+        <v>7976</v>
+      </c>
+      <c r="E47" t="n">
+        <v>9330</v>
+      </c>
+      <c r="F47" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="H47" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I47" t="n">
+        <v>10474</v>
+      </c>
+      <c r="J47" t="n">
+        <v>6875</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>16376</v>
+      </c>
+      <c r="M47" t="n">
+        <v>12410</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>81130</v>
+      </c>
+      <c r="P47" t="n">
+        <v>70677</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R47" t="n">
+        <v>16218</v>
+      </c>
+      <c r="S47" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T47" t="n">
+        <v>16376</v>
+      </c>
+      <c r="U47" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W47" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X47" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB47"/>
+  <dimension ref="A1:AB48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4680,6 +4680,96 @@
         </is>
       </c>
       <c r="AB47" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>17:26:55</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D48" t="n">
+        <v>7969</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9322</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="H48" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3595</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-6879</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-12376</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>83023</v>
+      </c>
+      <c r="P48" t="n">
+        <v>62855</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R48" t="n">
+        <v>16221</v>
+      </c>
+      <c r="S48" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T48" t="n">
+        <v>16413</v>
+      </c>
+      <c r="U48" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X48" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB48"/>
+  <dimension ref="A1:AB49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4770,6 +4770,96 @@
         </is>
       </c>
       <c r="AB48" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>17:27:57</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D49" t="n">
+        <v>7978</v>
+      </c>
+      <c r="E49" t="n">
+        <v>9323</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="H49" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I49" t="n">
+        <v>10479</v>
+      </c>
+      <c r="J49" t="n">
+        <v>6884</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>16356</v>
+      </c>
+      <c r="M49" t="n">
+        <v>12356</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>81332</v>
+      </c>
+      <c r="P49" t="n">
+        <v>70679</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R49" t="n">
+        <v>16215</v>
+      </c>
+      <c r="S49" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T49" t="n">
+        <v>16356</v>
+      </c>
+      <c r="U49" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W49" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X49" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB49"/>
+  <dimension ref="A1:AB50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4860,6 +4860,96 @@
         </is>
       </c>
       <c r="AB49" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>17:28:58</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D50" t="n">
+        <v>7983</v>
+      </c>
+      <c r="E50" t="n">
+        <v>9306</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="H50" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I50" t="n">
+        <v>10578</v>
+      </c>
+      <c r="J50" t="n">
+        <v>99</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>16432</v>
+      </c>
+      <c r="M50" t="n">
+        <v>76</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>81585</v>
+      </c>
+      <c r="P50" t="n">
+        <v>70629</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R50" t="n">
+        <v>16226</v>
+      </c>
+      <c r="S50" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T50" t="n">
+        <v>16432</v>
+      </c>
+      <c r="U50" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W50" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X50" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB50"/>
+  <dimension ref="A1:AB51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4950,6 +4950,96 @@
         </is>
       </c>
       <c r="AB50" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>17:29:59</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D51" t="n">
+        <v>7983</v>
+      </c>
+      <c r="E51" t="n">
+        <v>9302</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="H51" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I51" t="n">
+        <v>10593</v>
+      </c>
+      <c r="J51" t="n">
+        <v>15</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>16428</v>
+      </c>
+      <c r="M51" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>81641</v>
+      </c>
+      <c r="P51" t="n">
+        <v>70689</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R51" t="n">
+        <v>16218</v>
+      </c>
+      <c r="S51" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T51" t="n">
+        <v>16428</v>
+      </c>
+      <c r="U51" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="W51" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X51" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB51"/>
+  <dimension ref="A1:AB52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5040,6 +5040,96 @@
         </is>
       </c>
       <c r="AB51" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>17:31:00</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D52" t="n">
+        <v>7975</v>
+      </c>
+      <c r="E52" t="n">
+        <v>9324</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3699</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-6894</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>4144</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-12284</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>83543</v>
+      </c>
+      <c r="P52" t="n">
+        <v>62898</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R52" t="n">
+        <v>16216</v>
+      </c>
+      <c r="S52" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T52" t="n">
+        <v>16458</v>
+      </c>
+      <c r="U52" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W52" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X52" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB52"/>
+  <dimension ref="A1:AB53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5130,6 +5130,96 @@
         </is>
       </c>
       <c r="AB52" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>17:32:01</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D53" t="n">
+        <v>7966</v>
+      </c>
+      <c r="E53" t="n">
+        <v>9328</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="H53" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3711</v>
+      </c>
+      <c r="J53" t="n">
+        <v>12</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>4223</v>
+      </c>
+      <c r="M53" t="n">
+        <v>79</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>83428</v>
+      </c>
+      <c r="P53" t="n">
+        <v>63164</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R53" t="n">
+        <v>16236</v>
+      </c>
+      <c r="S53" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T53" t="n">
+        <v>16608</v>
+      </c>
+      <c r="U53" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="W53" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X53" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB53"/>
+  <dimension ref="A1:AB54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5220,6 +5220,96 @@
         </is>
       </c>
       <c r="AB53" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>17:33:02</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D54" t="n">
+        <v>7971</v>
+      </c>
+      <c r="E54" t="n">
+        <v>9329</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="H54" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3732</v>
+      </c>
+      <c r="J54" t="n">
+        <v>21</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>4238</v>
+      </c>
+      <c r="M54" t="n">
+        <v>15</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>83609</v>
+      </c>
+      <c r="P54" t="n">
+        <v>63211</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R54" t="n">
+        <v>16268</v>
+      </c>
+      <c r="S54" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T54" t="n">
+        <v>16617</v>
+      </c>
+      <c r="U54" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W54" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X54" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB54"/>
+  <dimension ref="A1:AB55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5310,6 +5310,96 @@
         </is>
       </c>
       <c r="AB54" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>17:34:04</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>7964</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9331</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="H55" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3680</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-52</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>4267</v>
+      </c>
+      <c r="M55" t="n">
+        <v>29</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>83223</v>
+      </c>
+      <c r="P55" t="n">
+        <v>63341</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R55" t="n">
+        <v>16269</v>
+      </c>
+      <c r="S55" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T55" t="n">
+        <v>16621</v>
+      </c>
+      <c r="U55" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="W55" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X55" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB55"/>
+  <dimension ref="A1:AB56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5400,6 +5400,96 @@
         </is>
       </c>
       <c r="AB55" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>17:35:05</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D56" t="n">
+        <v>7975</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9317</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="H56" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3709</v>
+      </c>
+      <c r="J56" t="n">
+        <v>29</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>4244</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-23</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>83462</v>
+      </c>
+      <c r="P56" t="n">
+        <v>63291</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R56" t="n">
+        <v>16276</v>
+      </c>
+      <c r="S56" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T56" t="n">
+        <v>16638</v>
+      </c>
+      <c r="U56" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="W56" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X56" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB56"/>
+  <dimension ref="A1:AB57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5495,6 +5495,96 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>17:36:06</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D57" t="n">
+        <v>7978</v>
+      </c>
+      <c r="E57" t="n">
+        <v>9317</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="H57" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I57" t="n">
+        <v>10486</v>
+      </c>
+      <c r="J57" t="n">
+        <v>6777</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>16556</v>
+      </c>
+      <c r="M57" t="n">
+        <v>12312</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>81638</v>
+      </c>
+      <c r="P57" t="n">
+        <v>71116</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R57" t="n">
+        <v>16328</v>
+      </c>
+      <c r="S57" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T57" t="n">
+        <v>16556</v>
+      </c>
+      <c r="U57" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="W57" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X57" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB57"/>
+  <dimension ref="A1:AB58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5585,6 +5585,96 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>17:37:07</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7983</v>
+      </c>
+      <c r="E58" t="n">
+        <v>9313</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H58" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I58" t="n">
+        <v>10492</v>
+      </c>
+      <c r="J58" t="n">
+        <v>6</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>16493</v>
+      </c>
+      <c r="M58" t="n">
+        <v>-63</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>81652</v>
+      </c>
+      <c r="P58" t="n">
+        <v>70990</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R58" t="n">
+        <v>16297</v>
+      </c>
+      <c r="S58" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T58" t="n">
+        <v>16493</v>
+      </c>
+      <c r="U58" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X58" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB58"/>
+  <dimension ref="A1:AB59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5675,6 +5675,96 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>17:38:08</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D59" t="n">
+        <v>7982</v>
+      </c>
+      <c r="E59" t="n">
+        <v>9298</v>
+      </c>
+      <c r="F59" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="H59" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>10531</v>
+      </c>
+      <c r="J59" t="n">
+        <v>39</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>16553</v>
+      </c>
+      <c r="M59" t="n">
+        <v>60</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>81907</v>
+      </c>
+      <c r="P59" t="n">
+        <v>71012</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R59" t="n">
+        <v>16428</v>
+      </c>
+      <c r="S59" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T59" t="n">
+        <v>16553</v>
+      </c>
+      <c r="U59" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="W59" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X59" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB59"/>
+  <dimension ref="A1:AB60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5765,6 +5765,90 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>17:38:51</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D60" t="n">
+        <v>7977</v>
+      </c>
+      <c r="E60" t="n">
+        <v>9308</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="H60" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I60" t="n">
+        <v>10572</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>16542</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>81890</v>
+      </c>
+      <c r="P60" t="n">
+        <v>71002</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R60" t="n">
+        <v>16414</v>
+      </c>
+      <c r="S60" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T60" t="n">
+        <v>16542</v>
+      </c>
+      <c r="U60" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="W60" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X60" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB60"/>
+  <dimension ref="A1:AB61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5849,6 +5849,90 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>17:39:06</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D61" t="n">
+        <v>7977</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9308</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="H61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I61" t="n">
+        <v>10574</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>16610</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>81924</v>
+      </c>
+      <c r="P61" t="n">
+        <v>71091</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R61" t="n">
+        <v>16414</v>
+      </c>
+      <c r="S61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T61" t="n">
+        <v>16610</v>
+      </c>
+      <c r="U61" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="W61" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X61" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB61"/>
+  <dimension ref="A1:AB62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5933,6 +5933,96 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>17:40:07</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7989</v>
+      </c>
+      <c r="E62" t="n">
+        <v>9287</v>
+      </c>
+      <c r="F62" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="H62" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I62" t="n">
+        <v>10509</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-65</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>16433</v>
+      </c>
+      <c r="M62" t="n">
+        <v>-177</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>81947</v>
+      </c>
+      <c r="P62" t="n">
+        <v>70417</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R62" t="n">
+        <v>16388</v>
+      </c>
+      <c r="S62" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T62" t="n">
+        <v>16433</v>
+      </c>
+      <c r="U62" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="W62" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X62" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB62"/>
+  <dimension ref="A1:AB63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6023,6 +6023,96 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>17:41:08</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D63" t="n">
+        <v>7982</v>
+      </c>
+      <c r="E63" t="n">
+        <v>9295</v>
+      </c>
+      <c r="F63" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="H63" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I63" t="n">
+        <v>10595</v>
+      </c>
+      <c r="J63" t="n">
+        <v>86</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>16510</v>
+      </c>
+      <c r="M63" t="n">
+        <v>77</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>81888</v>
+      </c>
+      <c r="P63" t="n">
+        <v>70653</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R63" t="n">
+        <v>16371</v>
+      </c>
+      <c r="S63" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T63" t="n">
+        <v>16510</v>
+      </c>
+      <c r="U63" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="W63" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X63" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB63"/>
+  <dimension ref="A1:AB64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6113,6 +6113,96 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>17:42:10</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D64" t="n">
+        <v>7977</v>
+      </c>
+      <c r="E64" t="n">
+        <v>9286</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H64" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I64" t="n">
+        <v>10593</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>16522</v>
+      </c>
+      <c r="M64" t="n">
+        <v>12</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>81969</v>
+      </c>
+      <c r="P64" t="n">
+        <v>70662</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R64" t="n">
+        <v>16390</v>
+      </c>
+      <c r="S64" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T64" t="n">
+        <v>16522</v>
+      </c>
+      <c r="U64" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="W64" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X64" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB64"/>
+  <dimension ref="A1:AB65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6203,6 +6203,96 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>17:43:11</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D65" t="n">
+        <v>7980</v>
+      </c>
+      <c r="E65" t="n">
+        <v>9285</v>
+      </c>
+      <c r="F65" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="H65" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I65" t="n">
+        <v>10586</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>16505</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-17</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>81971</v>
+      </c>
+      <c r="P65" t="n">
+        <v>70554</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R65" t="n">
+        <v>16421</v>
+      </c>
+      <c r="S65" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T65" t="n">
+        <v>16505</v>
+      </c>
+      <c r="U65" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="W65" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X65" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB65"/>
+  <dimension ref="A1:AB66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6293,6 +6293,96 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>17:44:12</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D66" t="n">
+        <v>7981</v>
+      </c>
+      <c r="E66" t="n">
+        <v>9290</v>
+      </c>
+      <c r="F66" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="H66" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I66" t="n">
+        <v>10581</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>16507</v>
+      </c>
+      <c r="M66" t="n">
+        <v>2</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>82124</v>
+      </c>
+      <c r="P66" t="n">
+        <v>70444</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R66" t="n">
+        <v>16437</v>
+      </c>
+      <c r="S66" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T66" t="n">
+        <v>16507</v>
+      </c>
+      <c r="U66" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="W66" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X66" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB66"/>
+  <dimension ref="A1:AB67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6383,6 +6383,96 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>17:45:13</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D67" t="n">
+        <v>7980</v>
+      </c>
+      <c r="E67" t="n">
+        <v>9292</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="H67" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I67" t="n">
+        <v>10637</v>
+      </c>
+      <c r="J67" t="n">
+        <v>56</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>16460</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-47</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>82371</v>
+      </c>
+      <c r="P67" t="n">
+        <v>70303</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R67" t="n">
+        <v>16439</v>
+      </c>
+      <c r="S67" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T67" t="n">
+        <v>16460</v>
+      </c>
+      <c r="U67" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="W67" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X67" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB67"/>
+  <dimension ref="A1:AB68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6473,6 +6473,96 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>17:46:14</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D68" t="n">
+        <v>7979</v>
+      </c>
+      <c r="E68" t="n">
+        <v>9292</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="H68" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I68" t="n">
+        <v>10690</v>
+      </c>
+      <c r="J68" t="n">
+        <v>53</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>16527</v>
+      </c>
+      <c r="M68" t="n">
+        <v>67</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>82425</v>
+      </c>
+      <c r="P68" t="n">
+        <v>70325</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R68" t="n">
+        <v>16443</v>
+      </c>
+      <c r="S68" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T68" t="n">
+        <v>16527</v>
+      </c>
+      <c r="U68" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="W68" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X68" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB68"/>
+  <dimension ref="A1:AB69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6563,6 +6563,96 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>17:47:16</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D69" t="n">
+        <v>7980</v>
+      </c>
+      <c r="E69" t="n">
+        <v>9286</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="H69" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I69" t="n">
+        <v>10707</v>
+      </c>
+      <c r="J69" t="n">
+        <v>17</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>16460</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-67</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>82401</v>
+      </c>
+      <c r="P69" t="n">
+        <v>70117</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R69" t="n">
+        <v>16447</v>
+      </c>
+      <c r="S69" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T69" t="n">
+        <v>16460</v>
+      </c>
+      <c r="U69" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W69" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X69" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB69"/>
+  <dimension ref="A1:AB70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6653,6 +6653,96 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>17:48:17</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D70" t="n">
+        <v>7979</v>
+      </c>
+      <c r="E70" t="n">
+        <v>9279</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H70" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I70" t="n">
+        <v>10758</v>
+      </c>
+      <c r="J70" t="n">
+        <v>51</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>16419</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-41</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>82465</v>
+      </c>
+      <c r="P70" t="n">
+        <v>69915</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R70" t="n">
+        <v>16433</v>
+      </c>
+      <c r="S70" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T70" t="n">
+        <v>16419</v>
+      </c>
+      <c r="U70" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W70" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X70" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB70"/>
+  <dimension ref="A1:AB71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6743,6 +6743,96 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>17:49:18</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D71" t="n">
+        <v>7983</v>
+      </c>
+      <c r="E71" t="n">
+        <v>9325</v>
+      </c>
+      <c r="F71" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="H71" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I71" t="n">
+        <v>10875</v>
+      </c>
+      <c r="J71" t="n">
+        <v>117</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>16317</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-102</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>82681</v>
+      </c>
+      <c r="P71" t="n">
+        <v>69358</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R71" t="n">
+        <v>16434</v>
+      </c>
+      <c r="S71" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T71" t="n">
+        <v>16317</v>
+      </c>
+      <c r="U71" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="W71" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X71" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB71"/>
+  <dimension ref="A1:AB72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6833,6 +6833,96 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>17:50:20</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D72" t="n">
+        <v>7983</v>
+      </c>
+      <c r="E72" t="n">
+        <v>9324</v>
+      </c>
+      <c r="F72" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="H72" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I72" t="n">
+        <v>10920</v>
+      </c>
+      <c r="J72" t="n">
+        <v>45</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>16386</v>
+      </c>
+      <c r="M72" t="n">
+        <v>69</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>82920</v>
+      </c>
+      <c r="P72" t="n">
+        <v>69227</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R72" t="n">
+        <v>16463</v>
+      </c>
+      <c r="S72" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T72" t="n">
+        <v>16386</v>
+      </c>
+      <c r="U72" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="W72" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X72" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB72"/>
+  <dimension ref="A1:AB73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6923,6 +6923,96 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>17:51:21</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D73" t="n">
+        <v>7975</v>
+      </c>
+      <c r="E73" t="n">
+        <v>9333</v>
+      </c>
+      <c r="F73" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1.381</v>
+      </c>
+      <c r="H73" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I73" t="n">
+        <v>3944</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-6976</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>4027</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-12359</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>84484</v>
+      </c>
+      <c r="P73" t="n">
+        <v>61179</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R73" t="n">
+        <v>16457</v>
+      </c>
+      <c r="S73" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T73" t="n">
+        <v>16258</v>
+      </c>
+      <c r="U73" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="W73" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X73" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB73"/>
+  <dimension ref="A1:AB74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7013,6 +7013,96 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>17:52:22</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D74" t="n">
+        <v>7977</v>
+      </c>
+      <c r="E74" t="n">
+        <v>9333</v>
+      </c>
+      <c r="F74" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1.196</v>
+      </c>
+      <c r="H74" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I74" t="n">
+        <v>10842</v>
+      </c>
+      <c r="J74" t="n">
+        <v>6898</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>16231</v>
+      </c>
+      <c r="M74" t="n">
+        <v>12204</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>82681</v>
+      </c>
+      <c r="P74" t="n">
+        <v>69110</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R74" t="n">
+        <v>16488</v>
+      </c>
+      <c r="S74" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T74" t="n">
+        <v>16231</v>
+      </c>
+      <c r="U74" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="W74" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X74" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB74"/>
+  <dimension ref="A1:AB75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7103,6 +7103,96 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>17:53:23</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7978</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9332</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="H75" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I75" t="n">
+        <v>10848</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>16279</v>
+      </c>
+      <c r="M75" t="n">
+        <v>48</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>82662</v>
+      </c>
+      <c r="P75" t="n">
+        <v>69233</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R75" t="n">
+        <v>16494</v>
+      </c>
+      <c r="S75" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T75" t="n">
+        <v>16279</v>
+      </c>
+      <c r="U75" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="W75" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X75" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB75"/>
+  <dimension ref="A1:AB76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7193,6 +7193,96 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>17:54:24</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D76" t="n">
+        <v>7982</v>
+      </c>
+      <c r="E76" t="n">
+        <v>9327</v>
+      </c>
+      <c r="F76" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="H76" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I76" t="n">
+        <v>10881</v>
+      </c>
+      <c r="J76" t="n">
+        <v>33</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>16241</v>
+      </c>
+      <c r="M76" t="n">
+        <v>-38</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>82811</v>
+      </c>
+      <c r="P76" t="n">
+        <v>69122</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R76" t="n">
+        <v>16543</v>
+      </c>
+      <c r="S76" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T76" t="n">
+        <v>16241</v>
+      </c>
+      <c r="U76" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="W76" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X76" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB76"/>
+  <dimension ref="A1:AB77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7283,6 +7283,96 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>17:55:26</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D77" t="n">
+        <v>7984</v>
+      </c>
+      <c r="E77" t="n">
+        <v>9320</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="H77" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I77" t="n">
+        <v>10932</v>
+      </c>
+      <c r="J77" t="n">
+        <v>51</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>16229</v>
+      </c>
+      <c r="M77" t="n">
+        <v>-12</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>83089</v>
+      </c>
+      <c r="P77" t="n">
+        <v>69096</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R77" t="n">
+        <v>16635</v>
+      </c>
+      <c r="S77" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T77" t="n">
+        <v>16229</v>
+      </c>
+      <c r="U77" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="W77" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X77" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB77"/>
+  <dimension ref="A1:AB78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7373,6 +7373,96 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>17:56:28</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D78" t="n">
+        <v>7974</v>
+      </c>
+      <c r="E78" t="n">
+        <v>9314</v>
+      </c>
+      <c r="F78" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1.384</v>
+      </c>
+      <c r="H78" t="n">
+        <v>7950</v>
+      </c>
+      <c r="I78" t="n">
+        <v>3938</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-6994</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>3961</v>
+      </c>
+      <c r="M78" t="n">
+        <v>-12268</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>84974</v>
+      </c>
+      <c r="P78" t="n">
+        <v>61386</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R78" t="n">
+        <v>16623</v>
+      </c>
+      <c r="S78" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T78" t="n">
+        <v>16354</v>
+      </c>
+      <c r="U78" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="W78" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X78" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB78"/>
+  <dimension ref="A1:AB79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7463,6 +7463,96 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>17:57:29</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D79" t="n">
+        <v>7979</v>
+      </c>
+      <c r="E79" t="n">
+        <v>9312</v>
+      </c>
+      <c r="F79" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I79" t="n">
+        <v>11032</v>
+      </c>
+      <c r="J79" t="n">
+        <v>7094</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>16422</v>
+      </c>
+      <c r="M79" t="n">
+        <v>12461</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>83136</v>
+      </c>
+      <c r="P79" t="n">
+        <v>69293</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R79" t="n">
+        <v>16622</v>
+      </c>
+      <c r="S79" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T79" t="n">
+        <v>16422</v>
+      </c>
+      <c r="U79" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="W79" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X79" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB79"/>
+  <dimension ref="A1:AB80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7553,6 +7553,96 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>17:58:30</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D80" t="n">
+        <v>7982</v>
+      </c>
+      <c r="E80" t="n">
+        <v>9307</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="H80" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I80" t="n">
+        <v>11075</v>
+      </c>
+      <c r="J80" t="n">
+        <v>43</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>16365</v>
+      </c>
+      <c r="M80" t="n">
+        <v>-57</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>83250</v>
+      </c>
+      <c r="P80" t="n">
+        <v>69160</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R80" t="n">
+        <v>16636</v>
+      </c>
+      <c r="S80" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T80" t="n">
+        <v>16365</v>
+      </c>
+      <c r="U80" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="W80" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X80" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB80"/>
+  <dimension ref="A1:AB81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7643,6 +7643,96 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>17:59:31</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D81" t="n">
+        <v>7982</v>
+      </c>
+      <c r="E81" t="n">
+        <v>9339</v>
+      </c>
+      <c r="F81" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="H81" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I81" t="n">
+        <v>11101</v>
+      </c>
+      <c r="J81" t="n">
+        <v>26</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>16337</v>
+      </c>
+      <c r="M81" t="n">
+        <v>-28</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>83361</v>
+      </c>
+      <c r="P81" t="n">
+        <v>69181</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R81" t="n">
+        <v>16637</v>
+      </c>
+      <c r="S81" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T81" t="n">
+        <v>16337</v>
+      </c>
+      <c r="U81" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="W81" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X81" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB81"/>
+  <dimension ref="A1:AB82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7733,6 +7733,96 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>18:00:32</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D82" t="n">
+        <v>7990</v>
+      </c>
+      <c r="E82" t="n">
+        <v>9327</v>
+      </c>
+      <c r="F82" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1.206</v>
+      </c>
+      <c r="H82" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I82" t="n">
+        <v>11153</v>
+      </c>
+      <c r="J82" t="n">
+        <v>52</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>16329</v>
+      </c>
+      <c r="M82" t="n">
+        <v>-8</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>83437</v>
+      </c>
+      <c r="P82" t="n">
+        <v>69181</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R82" t="n">
+        <v>16644</v>
+      </c>
+      <c r="S82" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T82" t="n">
+        <v>16329</v>
+      </c>
+      <c r="U82" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="W82" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X82" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB82"/>
+  <dimension ref="A1:AB83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7823,6 +7823,96 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>18:01:33</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D83" t="n">
+        <v>7985</v>
+      </c>
+      <c r="E83" t="n">
+        <v>9302</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1.221</v>
+      </c>
+      <c r="H83" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I83" t="n">
+        <v>11239</v>
+      </c>
+      <c r="J83" t="n">
+        <v>86</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>16163</v>
+      </c>
+      <c r="M83" t="n">
+        <v>-166</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>83698</v>
+      </c>
+      <c r="P83" t="n">
+        <v>68534</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R83" t="n">
+        <v>16704</v>
+      </c>
+      <c r="S83" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T83" t="n">
+        <v>16163</v>
+      </c>
+      <c r="U83" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="W83" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X83" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>7950</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB83"/>
+  <dimension ref="A1:AB84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7913,6 +7913,90 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>18:49:08</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="D84" t="n">
+        <v>7891</v>
+      </c>
+      <c r="E84" t="n">
+        <v>9262</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1.313</v>
+      </c>
+      <c r="H84" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I84" t="n">
+        <v>9867</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>8619</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>87729</v>
+      </c>
+      <c r="P84" t="n">
+        <v>66818</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R84" t="n">
+        <v>16165</v>
+      </c>
+      <c r="S84" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T84" t="n">
+        <v>17263</v>
+      </c>
+      <c r="U84" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="W84" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X84" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB84"/>
+  <dimension ref="A1:AB85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7997,6 +7997,96 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>18:50:09</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="D85" t="n">
+        <v>7890</v>
+      </c>
+      <c r="E85" t="n">
+        <v>9264</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="H85" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I85" t="n">
+        <v>9656</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-211</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>8728</v>
+      </c>
+      <c r="M85" t="n">
+        <v>109</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>87249</v>
+      </c>
+      <c r="P85" t="n">
+        <v>67716</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R85" t="n">
+        <v>16132</v>
+      </c>
+      <c r="S85" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T85" t="n">
+        <v>17283</v>
+      </c>
+      <c r="U85" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="W85" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X85" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB85"/>
+  <dimension ref="A1:AB86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8087,6 +8087,96 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>18:51:11</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="D86" t="n">
+        <v>7885</v>
+      </c>
+      <c r="E86" t="n">
+        <v>9233</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="H86" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I86" t="n">
+        <v>9720</v>
+      </c>
+      <c r="J86" t="n">
+        <v>64</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>8856</v>
+      </c>
+      <c r="M86" t="n">
+        <v>128</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>87017</v>
+      </c>
+      <c r="P86" t="n">
+        <v>67804</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R86" t="n">
+        <v>16124</v>
+      </c>
+      <c r="S86" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T86" t="n">
+        <v>17154</v>
+      </c>
+      <c r="U86" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="W86" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X86" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB86"/>
+  <dimension ref="A1:AB87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8177,6 +8177,96 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>18:52:13</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="D87" t="n">
+        <v>7894</v>
+      </c>
+      <c r="E87" t="n">
+        <v>9209</v>
+      </c>
+      <c r="F87" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="H87" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I87" t="n">
+        <v>9847</v>
+      </c>
+      <c r="J87" t="n">
+        <v>127</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>8903</v>
+      </c>
+      <c r="M87" t="n">
+        <v>47</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>87508</v>
+      </c>
+      <c r="P87" t="n">
+        <v>67935</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R87" t="n">
+        <v>16127</v>
+      </c>
+      <c r="S87" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T87" t="n">
+        <v>17160</v>
+      </c>
+      <c r="U87" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="W87" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X87" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB87"/>
+  <dimension ref="A1:AB88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8267,6 +8267,96 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>18:53:14</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="D88" t="n">
+        <v>7896</v>
+      </c>
+      <c r="E88" t="n">
+        <v>9206</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="H88" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I88" t="n">
+        <v>9962</v>
+      </c>
+      <c r="J88" t="n">
+        <v>115</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>8952</v>
+      </c>
+      <c r="M88" t="n">
+        <v>49</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>88067</v>
+      </c>
+      <c r="P88" t="n">
+        <v>67975</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R88" t="n">
+        <v>16154</v>
+      </c>
+      <c r="S88" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T88" t="n">
+        <v>17088</v>
+      </c>
+      <c r="U88" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W88" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X88" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB88"/>
+  <dimension ref="A1:AB89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8357,6 +8357,96 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>18:54:15</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="D89" t="n">
+        <v>7890</v>
+      </c>
+      <c r="E89" t="n">
+        <v>9216</v>
+      </c>
+      <c r="F89" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="H89" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I89" t="n">
+        <v>9893</v>
+      </c>
+      <c r="J89" t="n">
+        <v>-69</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>8986</v>
+      </c>
+      <c r="M89" t="n">
+        <v>34</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>88132</v>
+      </c>
+      <c r="P89" t="n">
+        <v>68214</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R89" t="n">
+        <v>16179</v>
+      </c>
+      <c r="S89" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T89" t="n">
+        <v>17140</v>
+      </c>
+      <c r="U89" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="W89" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X89" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB89"/>
+  <dimension ref="A1:AB90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8447,6 +8447,96 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>18:55:17</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D90" t="n">
+        <v>7892</v>
+      </c>
+      <c r="E90" t="n">
+        <v>9210</v>
+      </c>
+      <c r="F90" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="H90" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I90" t="n">
+        <v>9898</v>
+      </c>
+      <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>9014</v>
+      </c>
+      <c r="M90" t="n">
+        <v>28</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>88245</v>
+      </c>
+      <c r="P90" t="n">
+        <v>68312</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R90" t="n">
+        <v>16208</v>
+      </c>
+      <c r="S90" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T90" t="n">
+        <v>17171</v>
+      </c>
+      <c r="U90" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W90" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X90" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB90"/>
+  <dimension ref="A1:AB91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8537,6 +8537,96 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>18:56:18</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="D91" t="n">
+        <v>7902</v>
+      </c>
+      <c r="E91" t="n">
+        <v>9211</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="H91" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I91" t="n">
+        <v>9981</v>
+      </c>
+      <c r="J91" t="n">
+        <v>83</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>8950</v>
+      </c>
+      <c r="M91" t="n">
+        <v>-64</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>88260</v>
+      </c>
+      <c r="P91" t="n">
+        <v>67946</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R91" t="n">
+        <v>16227</v>
+      </c>
+      <c r="S91" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T91" t="n">
+        <v>17118</v>
+      </c>
+      <c r="U91" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W91" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X91" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB91"/>
+  <dimension ref="A1:AB92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8627,6 +8627,96 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>18:57:20</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D92" t="n">
+        <v>7892</v>
+      </c>
+      <c r="E92" t="n">
+        <v>9216</v>
+      </c>
+      <c r="F92" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="H92" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I92" t="n">
+        <v>9929</v>
+      </c>
+      <c r="J92" t="n">
+        <v>-52</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>8983</v>
+      </c>
+      <c r="M92" t="n">
+        <v>33</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>88212</v>
+      </c>
+      <c r="P92" t="n">
+        <v>68291</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R92" t="n">
+        <v>16215</v>
+      </c>
+      <c r="S92" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T92" t="n">
+        <v>17222</v>
+      </c>
+      <c r="U92" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W92" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X92" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB92"/>
+  <dimension ref="A1:AB93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8717,6 +8717,96 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>18:58:21</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="D93" t="n">
+        <v>7904</v>
+      </c>
+      <c r="E93" t="n">
+        <v>9211</v>
+      </c>
+      <c r="F93" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="H93" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I93" t="n">
+        <v>9976</v>
+      </c>
+      <c r="J93" t="n">
+        <v>47</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>8977</v>
+      </c>
+      <c r="M93" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>88494</v>
+      </c>
+      <c r="P93" t="n">
+        <v>68256</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R93" t="n">
+        <v>16256</v>
+      </c>
+      <c r="S93" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T93" t="n">
+        <v>17200</v>
+      </c>
+      <c r="U93" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W93" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X93" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB93"/>
+  <dimension ref="A1:AB94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8807,6 +8807,96 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>18:59:22</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="D94" t="n">
+        <v>7905</v>
+      </c>
+      <c r="E94" t="n">
+        <v>9221</v>
+      </c>
+      <c r="F94" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="H94" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I94" t="n">
+        <v>10068</v>
+      </c>
+      <c r="J94" t="n">
+        <v>92</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>8967</v>
+      </c>
+      <c r="M94" t="n">
+        <v>-10</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>88852</v>
+      </c>
+      <c r="P94" t="n">
+        <v>68207</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R94" t="n">
+        <v>16359</v>
+      </c>
+      <c r="S94" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T94" t="n">
+        <v>17197</v>
+      </c>
+      <c r="U94" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W94" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X94" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB94"/>
+  <dimension ref="A1:AB95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8897,6 +8897,96 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>19:00:24</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="D95" t="n">
+        <v>7896</v>
+      </c>
+      <c r="E95" t="n">
+        <v>9220</v>
+      </c>
+      <c r="F95" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="H95" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I95" t="n">
+        <v>9932</v>
+      </c>
+      <c r="J95" t="n">
+        <v>-136</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>9035</v>
+      </c>
+      <c r="M95" t="n">
+        <v>68</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>88441</v>
+      </c>
+      <c r="P95" t="n">
+        <v>68368</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R95" t="n">
+        <v>16339</v>
+      </c>
+      <c r="S95" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T95" t="n">
+        <v>17348</v>
+      </c>
+      <c r="U95" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W95" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X95" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB95"/>
+  <dimension ref="A1:AB96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8987,6 +8987,96 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>19:01:26</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="D96" t="n">
+        <v>7916</v>
+      </c>
+      <c r="E96" t="n">
+        <v>9202</v>
+      </c>
+      <c r="F96" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="H96" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I96" t="n">
+        <v>10028</v>
+      </c>
+      <c r="J96" t="n">
+        <v>96</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>8953</v>
+      </c>
+      <c r="M96" t="n">
+        <v>-82</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>88370</v>
+      </c>
+      <c r="P96" t="n">
+        <v>68011</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R96" t="n">
+        <v>16337</v>
+      </c>
+      <c r="S96" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T96" t="n">
+        <v>17248</v>
+      </c>
+      <c r="U96" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W96" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X96" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB96"/>
+  <dimension ref="A1:AB97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9077,6 +9077,96 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>19:02:27</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="D97" t="n">
+        <v>7916</v>
+      </c>
+      <c r="E97" t="n">
+        <v>9214</v>
+      </c>
+      <c r="F97" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="H97" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I97" t="n">
+        <v>9935</v>
+      </c>
+      <c r="J97" t="n">
+        <v>-93</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>8977</v>
+      </c>
+      <c r="M97" t="n">
+        <v>24</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>88289</v>
+      </c>
+      <c r="P97" t="n">
+        <v>68225</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R97" t="n">
+        <v>16383</v>
+      </c>
+      <c r="S97" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T97" t="n">
+        <v>17322</v>
+      </c>
+      <c r="U97" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W97" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X97" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB97"/>
+  <dimension ref="A1:AB98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9167,6 +9167,96 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>19:03:29</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="D98" t="n">
+        <v>7907</v>
+      </c>
+      <c r="E98" t="n">
+        <v>9214</v>
+      </c>
+      <c r="F98" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="H98" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I98" t="n">
+        <v>10072</v>
+      </c>
+      <c r="J98" t="n">
+        <v>137</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>9038</v>
+      </c>
+      <c r="M98" t="n">
+        <v>61</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>88428</v>
+      </c>
+      <c r="P98" t="n">
+        <v>68352</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R98" t="n">
+        <v>16390</v>
+      </c>
+      <c r="S98" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T98" t="n">
+        <v>17344</v>
+      </c>
+      <c r="U98" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="W98" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X98" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB98"/>
+  <dimension ref="A1:AB99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9257,6 +9257,96 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>19:04:30</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="D99" t="n">
+        <v>7906</v>
+      </c>
+      <c r="E99" t="n">
+        <v>9223</v>
+      </c>
+      <c r="F99" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="H99" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I99" t="n">
+        <v>10109</v>
+      </c>
+      <c r="J99" t="n">
+        <v>37</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>9040</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>88547</v>
+      </c>
+      <c r="P99" t="n">
+        <v>68409</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R99" t="n">
+        <v>16424</v>
+      </c>
+      <c r="S99" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T99" t="n">
+        <v>17373</v>
+      </c>
+      <c r="U99" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W99" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X99" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB99"/>
+  <dimension ref="A1:AB100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9347,6 +9347,96 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>19:05:32</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="D100" t="n">
+        <v>7901</v>
+      </c>
+      <c r="E100" t="n">
+        <v>9228</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="H100" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I100" t="n">
+        <v>10033</v>
+      </c>
+      <c r="J100" t="n">
+        <v>-76</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>9052</v>
+      </c>
+      <c r="M100" t="n">
+        <v>12</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>88411</v>
+      </c>
+      <c r="P100" t="n">
+        <v>68360</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R100" t="n">
+        <v>16379</v>
+      </c>
+      <c r="S100" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T100" t="n">
+        <v>17282</v>
+      </c>
+      <c r="U100" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="W100" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X100" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
+++ b/backend/signal_logs/2026-08-12/index_tracker_CRUDEOIL_2026-08-12.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB100"/>
+  <dimension ref="A1:AB101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9437,6 +9437,96 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>19:06:34</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="D101" t="n">
+        <v>7903</v>
+      </c>
+      <c r="E101" t="n">
+        <v>9235</v>
+      </c>
+      <c r="F101" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="H101" t="n">
+        <v>7900</v>
+      </c>
+      <c r="I101" t="n">
+        <v>10052</v>
+      </c>
+      <c r="J101" t="n">
+        <v>19</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>9096</v>
+      </c>
+      <c r="M101" t="n">
+        <v>44</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>88490</v>
+      </c>
+      <c r="P101" t="n">
+        <v>68647</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>7500</v>
+      </c>
+      <c r="R101" t="n">
+        <v>16400</v>
+      </c>
+      <c r="S101" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T101" t="n">
+        <v>17294</v>
+      </c>
+      <c r="U101" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="W101" t="n">
+        <v>7500</v>
+      </c>
+      <c r="X101" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>7900</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
